--- a/docs/downloads/05/tbl_house_status_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_house_status_marovoay_tous.xlsx
@@ -495,12 +495,6 @@
           <t>En location</t>
         </is>
       </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/docs/downloads/05/tbl_house_status_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_house_status_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
